--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.6040746786003</v>
+        <v>8.385662135272549</v>
       </c>
       <c r="D2" t="n">
-        <v>49.77574348637236</v>
+        <v>8.08855831653551</v>
       </c>
       <c r="E2" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F2" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.13457749757823</v>
+        <v>3.434368843356462</v>
       </c>
       <c r="D3" t="n">
-        <v>26.99797115050398</v>
+        <v>4.387170311956896</v>
       </c>
       <c r="E3" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F3" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.67459469604853</v>
+        <v>6.447121638107887</v>
       </c>
       <c r="D4" t="n">
-        <v>33.6905642530233</v>
+        <v>5.474716691116286</v>
       </c>
       <c r="E4" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F4" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.05658078008574</v>
+        <v>5.371694376763933</v>
       </c>
       <c r="D5" t="n">
-        <v>34.14095926797717</v>
+        <v>5.547905881046289</v>
       </c>
       <c r="E5" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F5" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.07849551336985</v>
+        <v>7.812755520922601</v>
       </c>
       <c r="D6" t="n">
-        <v>46.00093659699174</v>
+        <v>7.475152197011157</v>
       </c>
       <c r="E6" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F6" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.76694168813794</v>
+        <v>6.462128024322416</v>
       </c>
       <c r="D7" t="n">
-        <v>39.75666100975151</v>
+        <v>6.460457414084621</v>
       </c>
       <c r="E7" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F7" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.404866824891831</v>
+        <v>1.365790859044923</v>
       </c>
       <c r="D8" t="n">
-        <v>15.43060743031396</v>
+        <v>2.507473707426018</v>
       </c>
       <c r="E8" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F8" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.23048911990676</v>
+        <v>4.749954481984849</v>
       </c>
       <c r="D9" t="n">
-        <v>29.72033758398035</v>
+        <v>4.829554857396806</v>
       </c>
       <c r="E9" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F9" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.61460464172483</v>
+        <v>4.487373254280285</v>
       </c>
       <c r="D10" t="n">
-        <v>34.95151829925913</v>
+        <v>5.67962172362961</v>
       </c>
       <c r="E10" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F10" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.00940875127455</v>
+        <v>3.414028922082115</v>
       </c>
       <c r="D11" t="n">
-        <v>20.22561317708659</v>
+        <v>3.286662141276571</v>
       </c>
       <c r="E11" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F11" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>44.49050291227796</v>
+        <v>7.229706723245169</v>
       </c>
       <c r="D12" t="n">
-        <v>45.34290402266612</v>
+        <v>7.368221903683245</v>
       </c>
       <c r="E12" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F12" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>3.573644895656038</v>
+        <v>0.5807172955441062</v>
       </c>
       <c r="D13" t="n">
-        <v>4.09496714918716</v>
+        <v>0.6654321617429135</v>
       </c>
       <c r="E13" t="n">
-        <v>14.51270845244153</v>
+        <v>2.358315123521749</v>
       </c>
       <c r="F13" t="n">
-        <v>12.86855159336911</v>
+        <v>2.09113963392248</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
